--- a/Datas/__tables__.xlsx
+++ b/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -110,6 +110,9 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
+    <t>物品表</t>
+  </si>
+  <si>
     <t>item</t>
   </si>
   <si>
@@ -117,6 +120,138 @@
   </si>
   <si>
     <t>item@W-物品配置表.xlsx</t>
+  </si>
+  <si>
+    <t>战斗规则表</t>
+  </si>
+  <si>
+    <t>battle_rule</t>
+  </si>
+  <si>
+    <t>Ibattle_ruleConfig</t>
+  </si>
+  <si>
+    <t>battle_rule@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>卡牌表</t>
+  </si>
+  <si>
+    <t>card</t>
+  </si>
+  <si>
+    <t>IcardConfig</t>
+  </si>
+  <si>
+    <t>card@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>效果定义表</t>
+  </si>
+  <si>
+    <t>effect_define</t>
+  </si>
+  <si>
+    <t>Ieffect_defineConfig</t>
+  </si>
+  <si>
+    <t>effect_define@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>牌组表</t>
+  </si>
+  <si>
+    <t>deck</t>
+  </si>
+  <si>
+    <t>IdeckConfig</t>
+  </si>
+  <si>
+    <t>deck@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>牌组构成表</t>
+  </si>
+  <si>
+    <t>deck_card</t>
+  </si>
+  <si>
+    <t>Ideck_cardConfig</t>
+  </si>
+  <si>
+    <t>deck_card@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>武器表</t>
+  </si>
+  <si>
+    <t>weapon</t>
+  </si>
+  <si>
+    <t>IweaponConfig</t>
+  </si>
+  <si>
+    <t>weapon@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>敌人表</t>
+  </si>
+  <si>
+    <t>enemy</t>
+  </si>
+  <si>
+    <t>IenemyConfig</t>
+  </si>
+  <si>
+    <t>enemy@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>敌人意图表</t>
+  </si>
+  <si>
+    <t>enemy_intent</t>
+  </si>
+  <si>
+    <t>Ienemy_intentConfig</t>
+  </si>
+  <si>
+    <t>enemy_intent@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>场景配置表</t>
+  </si>
+  <si>
+    <t>combat_scenario</t>
+  </si>
+  <si>
+    <t>Icombat_scenarioConfig</t>
+  </si>
+  <si>
+    <t>combat_scenario@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>场景敌人配置表</t>
+  </si>
+  <si>
+    <t>combat_scenario_enemy</t>
+  </si>
+  <si>
+    <t>Icombat_scenario_enemyConfig</t>
+  </si>
+  <si>
+    <t>combat_scenario_enemy@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>状态表</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>IstatusConfig</t>
+  </si>
+  <si>
+    <t>status@B-战斗配置表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1080,12 +1215,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="1" width="15.475" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="44.375" customWidth="1"/>
+    <col min="4" max="4" width="48.2583333333333" customWidth="1"/>
     <col min="5" max="5" width="41.125" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
@@ -1180,23 +1316,224 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="item@W-物品配置表.xlsx" tooltip="mailto:item@W-物品配置表.xlsx"/>
+    <hyperlink ref="E5" r:id="rId2" display="battle_rule@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E6" r:id="rId3" display="card@B-战斗配置表.xlsx" tooltip="mailto:card@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E7" r:id="rId4" display="effect_define@B-战斗配置表.xlsx" tooltip="mailto:effect_define@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E8" r:id="rId5" display="deck@B-战斗配置表.xlsx" tooltip="mailto:deck@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E9" r:id="rId6" display="deck_card@B-战斗配置表.xlsx" tooltip="mailto:deck_card@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E10" r:id="rId7" display="weapon@B-战斗配置表.xlsx" tooltip="mailto:weapon@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E11" r:id="rId8" display="enemy@B-战斗配置表.xlsx" tooltip="mailto:enemy@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E12" r:id="rId9" display="enemy_intent@B-战斗配置表.xlsx" tooltip="mailto:enemy_intent@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E13" r:id="rId10" display="combat_scenario@B-战斗配置表.xlsx" tooltip="mailto:combat_scenario@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E14" r:id="rId11" display="combat_scenario_enemy@B-战斗配置表.xlsx" tooltip="mailto:combat_scenario_enemy@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E15" r:id="rId12" display="status@B-战斗配置表.xlsx" tooltip="mailto:status@B-战斗配置表.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__tables__.xlsx
+++ b/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -252,6 +252,18 @@
   </si>
   <si>
     <t>status@B-战斗配置表.xlsx</t>
+  </si>
+  <si>
+    <t>属性石表</t>
+  </si>
+  <si>
+    <t>element_stone</t>
+  </si>
+  <si>
+    <t>Ielement_stoneConfig</t>
+  </si>
+  <si>
+    <t>element_stone@B-战斗配置表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.475" customWidth="1"/>
@@ -1518,6 +1530,23 @@
       </c>
       <c r="E15" s="2" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1534,6 +1563,7 @@
     <hyperlink ref="E13" r:id="rId10" display="combat_scenario@B-战斗配置表.xlsx" tooltip="mailto:combat_scenario@B-战斗配置表.xlsx"/>
     <hyperlink ref="E14" r:id="rId11" display="combat_scenario_enemy@B-战斗配置表.xlsx" tooltip="mailto:combat_scenario_enemy@B-战斗配置表.xlsx"/>
     <hyperlink ref="E15" r:id="rId12" display="status@B-战斗配置表.xlsx" tooltip="mailto:status@B-战斗配置表.xlsx"/>
+    <hyperlink ref="E16" r:id="rId13" display="element_stone@B-战斗配置表.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
